--- a/source_data/workbooks/Source_Data_Fig3.xlsx
+++ b/source_data/workbooks/Source_Data_Fig3.xlsx
@@ -87,28 +87,28 @@
     <t>MedGemma</t>
   </si>
   <si>
+    <t>M3D</t>
+  </si>
+  <si>
+    <t>GPT-4o-vision</t>
+  </si>
+  <si>
+    <t>GPT-5-vision</t>
+  </si>
+  <si>
+    <t>GPT-5.4-vision</t>
+  </si>
+  <si>
+    <t>GPT-4o-agent</t>
+  </si>
+  <si>
     <t>MAM</t>
   </si>
   <si>
-    <t>M3D</t>
-  </si>
-  <si>
-    <t>GPT-4o-vision</t>
-  </si>
-  <si>
-    <t>GPT-5-vision</t>
-  </si>
-  <si>
-    <t>GPT-5.4-vision</t>
-  </si>
-  <si>
-    <t>GPT-4o-agent</t>
-  </si>
-  <si>
     <t>MedAgent-Pro</t>
   </si>
   <si>
-    <t>TLAgent</t>
+    <t>TissueLab</t>
   </si>
   <si>
     <t>accuracy</t>
@@ -738,7 +738,7 @@
         <v>226</v>
       </c>
       <c r="J4">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5894</v>
+        <v>0.5885</v>
       </c>
       <c r="O4">
         <v>0.7124</v>
       </c>
       <c r="P4">
-        <v>0.5894</v>
+        <v>0.5885</v>
       </c>
       <c r="Q4">
         <v>0.7124</v>
@@ -850,22 +850,22 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>0.6504</v>
+        <v>0.6584</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.0073</v>
       </c>
       <c r="N6">
-        <v>0.5885</v>
+        <v>0.5991</v>
       </c>
       <c r="O6">
-        <v>0.7124</v>
+        <v>0.7177</v>
       </c>
       <c r="P6">
-        <v>0.5885</v>
+        <v>0.5991</v>
       </c>
       <c r="Q6">
-        <v>0.7124</v>
+        <v>0.7177</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -903,22 +903,22 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>0.6584</v>
+        <v>0.4044</v>
       </c>
       <c r="M7">
-        <v>0.0073</v>
+        <v>0.0229</v>
       </c>
       <c r="N7">
-        <v>0.5991</v>
+        <v>0.3425</v>
       </c>
       <c r="O7">
-        <v>0.7177</v>
+        <v>0.4629</v>
       </c>
       <c r="P7">
-        <v>0.5991</v>
+        <v>0.3425</v>
       </c>
       <c r="Q7">
-        <v>0.7177</v>
+        <v>0.4629</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -956,22 +956,22 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>0.4044</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="M8">
-        <v>0.0229</v>
+        <v>0.0418</v>
       </c>
       <c r="N8">
-        <v>0.3425</v>
+        <v>0.5416</v>
       </c>
       <c r="O8">
-        <v>0.4629</v>
+        <v>0.6248</v>
       </c>
       <c r="P8">
-        <v>0.3425</v>
+        <v>0.5416</v>
       </c>
       <c r="Q8">
-        <v>0.4629</v>
+        <v>0.6248</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1003,28 +1003,28 @@
         <v>226</v>
       </c>
       <c r="J9">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>0.5832000000000001</v>
+        <v>0.6504</v>
       </c>
       <c r="M9">
-        <v>0.0418</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5416</v>
+        <v>0.5894</v>
       </c>
       <c r="O9">
-        <v>0.6248</v>
+        <v>0.7124</v>
       </c>
       <c r="P9">
-        <v>0.5416</v>
+        <v>0.5894</v>
       </c>
       <c r="Q9">
-        <v>0.6248</v>
+        <v>0.7124</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1345,28 +1345,28 @@
         <v>226</v>
       </c>
       <c r="J4">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>0.0134</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>-0.0359</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>-0.0359</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1457,22 +1457,22 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.1923</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>0.1923</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1510,22 +1510,22 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>0.1059</v>
+        <v>0.1576</v>
       </c>
       <c r="M7">
-        <v>0.044</v>
+        <v>0.0506</v>
       </c>
       <c r="N7">
-        <v>0.0138</v>
+        <v>0.1083</v>
       </c>
       <c r="O7">
-        <v>0.1923</v>
+        <v>0.2022</v>
       </c>
       <c r="P7">
-        <v>0.0138</v>
+        <v>0.1083</v>
       </c>
       <c r="Q7">
-        <v>0.1923</v>
+        <v>0.2022</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1563,22 +1563,22 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>0.1576</v>
+        <v>0.0202</v>
       </c>
       <c r="M8">
-        <v>0.0506</v>
+        <v>0.102</v>
       </c>
       <c r="N8">
-        <v>0.1083</v>
+        <v>-0.0435</v>
       </c>
       <c r="O8">
-        <v>0.2022</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P8">
-        <v>0.1083</v>
+        <v>-0.0435</v>
       </c>
       <c r="Q8">
-        <v>0.2022</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1610,28 +1610,28 @@
         <v>226</v>
       </c>
       <c r="J9">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>0.0202</v>
+        <v>0.0134</v>
       </c>
       <c r="M9">
-        <v>0.102</v>
+        <v>0.0133</v>
       </c>
       <c r="N9">
-        <v>-0.0435</v>
+        <v>-0.0359</v>
       </c>
       <c r="O9">
-        <v>0.08459999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="P9">
-        <v>-0.0435</v>
+        <v>-0.0359</v>
       </c>
       <c r="Q9">
-        <v>0.08459999999999999</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1952,28 +1952,28 @@
         <v>226</v>
       </c>
       <c r="J4">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>-0.0053</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0.009900000000000001</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>-0.0053</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.009900000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2064,22 +2064,22 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.0524</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.1051</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -2117,22 +2117,22 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>0.0524</v>
+        <v>0.0573</v>
       </c>
       <c r="M7">
-        <v>0.024</v>
+        <v>0.0275</v>
       </c>
       <c r="N7">
-        <v>0.0061</v>
+        <v>0.0331</v>
       </c>
       <c r="O7">
-        <v>0.1051</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="P7">
-        <v>0.0061</v>
+        <v>0.0331</v>
       </c>
       <c r="Q7">
-        <v>0.1051</v>
+        <v>0.08550000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2170,22 +2170,22 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>0.0573</v>
+        <v>0.0197</v>
       </c>
       <c r="M8">
-        <v>0.0275</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="N8">
-        <v>0.0331</v>
+        <v>-0.0421</v>
       </c>
       <c r="O8">
-        <v>0.08550000000000001</v>
+        <v>0.0822</v>
       </c>
       <c r="P8">
-        <v>0.0331</v>
+        <v>-0.0421</v>
       </c>
       <c r="Q8">
-        <v>0.08550000000000001</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2217,28 +2217,28 @@
         <v>226</v>
       </c>
       <c r="J9">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>0.0197</v>
+        <v>0.0015</v>
       </c>
       <c r="M9">
-        <v>0.09909999999999999</v>
+        <v>0.0034</v>
       </c>
       <c r="N9">
-        <v>-0.0421</v>
+        <v>-0.0053</v>
       </c>
       <c r="O9">
-        <v>0.0822</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P9">
-        <v>-0.0421</v>
+        <v>-0.0053</v>
       </c>
       <c r="Q9">
-        <v>0.0822</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2567,22 +2567,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.381</v>
+        <v>0.2381</v>
       </c>
       <c r="O4">
-        <v>0.7619</v>
+        <v>0.619</v>
       </c>
       <c r="P4">
-        <v>0.381</v>
+        <v>0.2381</v>
       </c>
       <c r="Q4">
-        <v>0.7619</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2620,22 +2620,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.2381</v>
+        <v>0.381</v>
       </c>
       <c r="O5">
-        <v>0.619</v>
+        <v>0.7619</v>
       </c>
       <c r="P5">
-        <v>0.2381</v>
+        <v>0.381</v>
       </c>
       <c r="Q5">
-        <v>0.619</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -2667,28 +2667,13 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0.381</v>
-      </c>
-      <c r="O6">
-        <v>0.7619</v>
-      </c>
-      <c r="P6">
-        <v>0.381</v>
-      </c>
-      <c r="Q6">
-        <v>0.7619</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -2720,13 +2705,28 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>0.0639</v>
+      </c>
+      <c r="N7">
+        <v>0.5429</v>
+      </c>
+      <c r="O7">
+        <v>0.7238</v>
+      </c>
+      <c r="P7">
+        <v>0.5429</v>
+      </c>
+      <c r="Q7">
+        <v>0.7238</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2758,28 +2758,28 @@
         <v>21</v>
       </c>
       <c r="J8">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M8">
-        <v>0.0639</v>
+        <v>0.0398</v>
       </c>
       <c r="N8">
-        <v>0.5429</v>
+        <v>0.1048</v>
       </c>
       <c r="O8">
-        <v>0.7238</v>
+        <v>0.2571</v>
       </c>
       <c r="P8">
-        <v>0.5429</v>
+        <v>0.1048</v>
       </c>
       <c r="Q8">
-        <v>0.7238</v>
+        <v>0.2571</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2811,28 +2811,28 @@
         <v>21</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M9">
-        <v>0.0398</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>0.1048</v>
+        <v>0.381</v>
       </c>
       <c r="O9">
-        <v>0.2571</v>
+        <v>0.7619</v>
       </c>
       <c r="P9">
-        <v>0.1048</v>
+        <v>0.381</v>
       </c>
       <c r="Q9">
-        <v>0.2571</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3261,28 +3261,13 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -3314,13 +3299,28 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>0.1427</v>
+      </c>
+      <c r="N7">
+        <v>0.0979</v>
+      </c>
+      <c r="O7">
+        <v>0.4544</v>
+      </c>
+      <c r="P7">
+        <v>0.0979</v>
+      </c>
+      <c r="Q7">
+        <v>0.4544</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3352,28 +3352,28 @@
         <v>21</v>
       </c>
       <c r="J8">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M8">
-        <v>0.1427</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>0.0979</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.4544</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0.0979</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3405,7 +3405,7 @@
         <v>21</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -3855,28 +3855,13 @@
         <v>21</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -3908,13 +3893,28 @@
         <v>21</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="M7">
+        <v>0.1333</v>
+      </c>
+      <c r="N7">
+        <v>0.092</v>
+      </c>
+      <c r="O7">
+        <v>0.4474</v>
+      </c>
+      <c r="P7">
+        <v>0.092</v>
+      </c>
+      <c r="Q7">
+        <v>0.4474</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3946,28 +3946,28 @@
         <v>21</v>
       </c>
       <c r="J8">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M8">
-        <v>0.1333</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.4474</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3999,7 +3999,7 @@
         <v>21</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <v>5</v>
